--- a/specific-profile-img/ig/StructureDefinition-fr-observation-transfusion-accidents-document.xlsx
+++ b/specific-profile-img/ig/StructureDefinition-fr-observation-transfusion-accidents-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:41:38+00:00</t>
+    <t>2026-07-31T07:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/specific-profile-img/ig/StructureDefinition-fr-observation-transfusion-accidents-document.xlsx
+++ b/specific-profile-img/ig/StructureDefinition-fr-observation-transfusion-accidents-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T07:56:22+00:00</t>
+    <t>2026-07-31T09:38:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/specific-profile-img/ig/StructureDefinition-fr-observation-transfusion-accidents-document.xlsx
+++ b/specific-profile-img/ig/StructureDefinition-fr-observation-transfusion-accidents-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T09:38:41+00:00</t>
+    <t>2026-07-31T12:59:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/specific-profile-img/ig/StructureDefinition-fr-observation-transfusion-accidents-document.xlsx
+++ b/specific-profile-img/ig/StructureDefinition-fr-observation-transfusion-accidents-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:59:03+00:00</t>
+    <t>2026-07-31T13:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/specific-profile-img/ig/StructureDefinition-fr-observation-transfusion-accidents-document.xlsx
+++ b/specific-profile-img/ig/StructureDefinition-fr-observation-transfusion-accidents-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:02:34+00:00</t>
+    <t>2026-07-31T13:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/specific-profile-img/ig/StructureDefinition-fr-observation-transfusion-accidents-document.xlsx
+++ b/specific-profile-img/ig/StructureDefinition-fr-observation-transfusion-accidents-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:07:52+00:00</t>
+    <t>2026-08-03T06:54:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
